--- a/data/sars/atlantic/tables/Atlantic_2010_Table1.xlsx
+++ b/data/sars/atlantic/tables/Atlantic_2010_Table1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/atlantic/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{463493B0-CBBF-4148-B5C9-7B15E449007F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4734061B-099A-2C4F-9A56-5D6F9799D231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="500" windowWidth="32680" windowHeight="21900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="110">
   <si>
     <t>Western North Atlantic</t>
   </si>
@@ -230,20 +230,6 @@
   </si>
   <si>
     <t>Puerto Rico and US Virgin Islands stock</t>
-  </si>
-  <si>
-    <r>
-      <t>928</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>j</t>
-    </r>
   </si>
   <si>
     <r>
@@ -825,49 +811,49 @@
   <sheetData>
     <row r="1" spans="1:20" ht="15" x14ac:dyDescent="0.15">
       <c r="A1" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="L1" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="M1" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="L1" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="O1" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="P1" s="1"/>
       <c r="S1" s="1"/>
@@ -875,7 +861,7 @@
     </row>
     <row r="2" spans="1:20" ht="15" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>0</v>
@@ -915,7 +901,7 @@
         <v>2</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P2" s="4"/>
       <c r="S2" s="2"/>
@@ -963,7 +949,7 @@
         <v>2</v>
       </c>
       <c r="O3" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P3" s="4"/>
       <c r="S3" s="2"/>
@@ -1011,7 +997,7 @@
         <v>2</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P4" s="4"/>
       <c r="S4" s="2"/>
@@ -1059,7 +1045,7 @@
         <v>2</v>
       </c>
       <c r="O5" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P5" s="9"/>
       <c r="S5" s="2"/>
@@ -1107,7 +1093,7 @@
         <v>2</v>
       </c>
       <c r="O6" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P6" s="4"/>
       <c r="S6" s="2"/>
@@ -1385,7 +1371,7 @@
     </row>
     <row r="13" spans="1:20" ht="15" x14ac:dyDescent="0.15">
       <c r="A13" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>0</v>
@@ -1430,7 +1416,7 @@
     </row>
     <row r="14" spans="1:20" ht="15" x14ac:dyDescent="0.15">
       <c r="A14" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>0</v>
@@ -1475,7 +1461,7 @@
     </row>
     <row r="15" spans="1:20" ht="15" x14ac:dyDescent="0.15">
       <c r="A15" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>0</v>
@@ -1518,7 +1504,7 @@
     </row>
     <row r="16" spans="1:20" ht="15" x14ac:dyDescent="0.15">
       <c r="A16" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>0</v>
@@ -1561,7 +1547,7 @@
     </row>
     <row r="17" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A17" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>0</v>
@@ -1604,7 +1590,7 @@
     </row>
     <row r="18" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A18" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>0</v>
@@ -1732,7 +1718,7 @@
         <v>2</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R20" s="4"/>
     </row>
@@ -1778,7 +1764,7 @@
         <v>2</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R21" s="4"/>
     </row>
@@ -1824,13 +1810,13 @@
         <v>2</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R22" s="4"/>
     </row>
     <row r="23" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>0</v>
@@ -1870,13 +1856,13 @@
         <v>2</v>
       </c>
       <c r="O23" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R23" s="4"/>
     </row>
     <row r="24" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A24" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>0</v>
@@ -1919,7 +1905,7 @@
     </row>
     <row r="25" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A25" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>0</v>
@@ -1959,7 +1945,7 @@
         <v>2</v>
       </c>
       <c r="O25" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R25" s="4"/>
     </row>
@@ -2010,7 +1996,7 @@
     </row>
     <row r="27" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A27" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>0</v>
@@ -2141,7 +2127,7 @@
     </row>
     <row r="30" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A30" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>0</v>
@@ -2310,7 +2296,7 @@
         <v>22</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R33" s="4"/>
     </row>
@@ -2319,7 +2305,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>16</v>
@@ -2356,7 +2342,7 @@
         <v>2</v>
       </c>
       <c r="O34" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R34" s="4"/>
     </row>
@@ -2365,7 +2351,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>16</v>
@@ -2402,7 +2388,7 @@
         <v>2</v>
       </c>
       <c r="O35" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R35" s="4"/>
     </row>
@@ -2411,7 +2397,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>16</v>
@@ -2448,7 +2434,7 @@
         <v>2</v>
       </c>
       <c r="O36" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R36" s="4"/>
     </row>
@@ -2494,7 +2480,7 @@
         <v>2</v>
       </c>
       <c r="O37" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R37" s="4"/>
     </row>
@@ -2540,7 +2526,7 @@
         <v>2</v>
       </c>
       <c r="O38" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R38" s="4"/>
     </row>
@@ -2586,7 +2572,7 @@
         <v>2</v>
       </c>
       <c r="O39" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R39" s="4"/>
     </row>
@@ -2632,7 +2618,7 @@
         <v>2</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R40" s="4"/>
     </row>
@@ -2684,7 +2670,7 @@
         <v>34</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>16</v>
@@ -2937,7 +2923,7 @@
       </c>
       <c r="R47" s="4"/>
     </row>
-    <row r="48" spans="1:18" ht="16" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A48" s="4" t="s">
         <v>50</v>
       </c>
@@ -2965,8 +2951,8 @@
       <c r="I48" s="8">
         <v>703</v>
       </c>
-      <c r="J48" s="4" t="s">
-        <v>69</v>
+      <c r="J48" s="4">
+        <v>928</v>
       </c>
       <c r="K48" s="4">
         <v>928</v>
@@ -2981,7 +2967,7 @@
         <v>2</v>
       </c>
       <c r="O48" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R48" s="4"/>
     </row>
@@ -3027,7 +3013,7 @@
         <v>2</v>
       </c>
       <c r="O49" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R49" s="4"/>
     </row>
@@ -3073,7 +3059,7 @@
         <v>2</v>
       </c>
       <c r="O50" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R50" s="4"/>
     </row>
@@ -3121,7 +3107,7 @@
         <v>2</v>
       </c>
       <c r="O51" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R51" s="4"/>
     </row>
@@ -3212,7 +3198,7 @@
         <v>2</v>
       </c>
       <c r="O53" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R53" s="4"/>
     </row>
@@ -3261,7 +3247,7 @@
     </row>
     <row r="55" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A55" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>56</v>
@@ -3304,7 +3290,7 @@
     </row>
     <row r="56" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A56" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>56</v>
@@ -3347,7 +3333,7 @@
     </row>
     <row r="57" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A57" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>56</v>
@@ -3473,7 +3459,7 @@
         <v>2</v>
       </c>
       <c r="O59" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R59" s="4"/>
     </row>
@@ -3519,7 +3505,7 @@
         <v>2</v>
       </c>
       <c r="O60" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R60" s="4"/>
     </row>
@@ -3565,7 +3551,7 @@
         <v>2</v>
       </c>
       <c r="O61" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R61" s="4"/>
     </row>
@@ -3638,7 +3624,7 @@
         <v>0.5</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J63" s="4" t="s">
         <v>12</v>
@@ -3654,7 +3640,7 @@
         <v>2</v>
       </c>
       <c r="O63" s="17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R63" s="4"/>
     </row>
@@ -3663,7 +3649,7 @@
         <v>28</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>16</v>
@@ -3703,7 +3689,7 @@
     </row>
     <row r="65" spans="1:20" ht="15" x14ac:dyDescent="0.15">
       <c r="A65" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>56</v>
@@ -3832,10 +3818,10 @@
     </row>
     <row r="68" spans="1:20" ht="15" x14ac:dyDescent="0.15">
       <c r="A68" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>16</v>
@@ -4001,7 +3987,7 @@
         <v>2</v>
       </c>
       <c r="O71" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R71" s="4"/>
     </row>
@@ -4262,13 +4248,13 @@
         <v>2</v>
       </c>
       <c r="O77" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R77" s="4"/>
     </row>
     <row r="78" spans="1:20" ht="16" x14ac:dyDescent="0.15">
       <c r="A78" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>56</v>
@@ -4352,7 +4338,7 @@
         <v>2</v>
       </c>
       <c r="O79" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R79" s="4"/>
       <c r="T79" s="2"/>
